--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirakiRyou\Desktop\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CA22E1-7215-4B81-B605-C364C63F5B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1B0A65-5346-4AFD-BF92-86747DEA7E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -230,6 +230,10 @@
     <rPh sb="27" eb="31">
       <t>ユウセンドヒク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オタカラアッタカラ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -565,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J14"/>
+  <dimension ref="B2:J163"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.875" customWidth="1"/>
@@ -704,6 +708,11 @@
         <v>6</v>
       </c>
     </row>
+    <row r="163" spans="10:10">
+      <c r="J163" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirakiRyou\Desktop\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Desktop\team_khhh\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1B0A65-5346-4AFD-BF92-86747DEA7E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="-12000" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
